--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N78_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N78_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.32479429912941</v>
+        <v>5.577779073608529</v>
       </c>
       <c r="D2" t="n">
-        <v>27.74891310222198</v>
+        <v>4.509198379111072</v>
       </c>
       <c r="E2" t="n">
-        <v>15.68756186493265</v>
+        <v>2.549228803051556</v>
       </c>
       <c r="F2" t="n">
-        <v>15.87157848825093</v>
+        <v>2.579131504340776</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>57.94507763301311</v>
+        <v>9.416075115364631</v>
       </c>
       <c r="D3" t="n">
-        <v>56.6722998730737</v>
+        <v>9.209248729374476</v>
       </c>
       <c r="E3" t="n">
-        <v>15.68756186493265</v>
+        <v>2.549228803051556</v>
       </c>
       <c r="F3" t="n">
-        <v>15.87157848825093</v>
+        <v>2.579131504340776</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.78233386259213</v>
+        <v>7.114629252671221</v>
       </c>
       <c r="D4" t="n">
-        <v>44.93806537145411</v>
+        <v>7.302435622861293</v>
       </c>
       <c r="E4" t="n">
-        <v>15.68756186493265</v>
+        <v>2.549228803051556</v>
       </c>
       <c r="F4" t="n">
-        <v>15.87157848825093</v>
+        <v>2.579131504340776</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.76207348226866</v>
+        <v>2.398836940868657</v>
       </c>
       <c r="D5" t="n">
-        <v>15.20590365303878</v>
+        <v>2.470959343618802</v>
       </c>
       <c r="E5" t="n">
-        <v>15.68756186493265</v>
+        <v>2.549228803051556</v>
       </c>
       <c r="F5" t="n">
-        <v>15.87157848825093</v>
+        <v>2.579131504340776</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
